--- a/reports/progression-report.xlsx
+++ b/reports/progression-report.xlsx
@@ -9,15 +9,14 @@
     <sheet sheetId="3" name="Усилие и откаты" state="visible" r:id="rId6"/>
     <sheet sheetId="4" name="Веса и повторы" state="visible" r:id="rId7"/>
     <sheet sheetId="5" name="Тест-кейсы" state="visible" r:id="rId8"/>
-    <sheet sheetId="6" name="Флоу конструктора" state="visible" r:id="rId9"/>
-    <sheet sheetId="7" name="Матчинг названий" state="visible" r:id="rId10"/>
+    <sheet sheetId="6" name="Матчинг названий" state="visible" r:id="rId9"/>
   </sheets>
   <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1981" uniqueCount="230">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1734" uniqueCount="179">
   <si>
     <t>Персона</t>
   </si>
@@ -244,6 +243,9 @@
     <t>10кг×15 / 10кг×15</t>
   </si>
   <si>
+    <t>7.5кг×15 / 7.5кг×15</t>
+  </si>
+  <si>
     <t>33кг×15 / 33кг×15</t>
   </si>
   <si>
@@ -349,6 +351,12 @@
     <t>15кг×20 / 15кг×20</t>
   </si>
   <si>
+    <t>22.5кг×12 / 22.5кг×12</t>
+  </si>
+  <si>
+    <t>20кг×12 / 20кг×12</t>
+  </si>
+  <si>
     <t>⚙ ассист · Подтягивания в гравитроне параллельный хват</t>
   </si>
   <si>
@@ -424,10 +432,10 @@
     <t>откатов не было в этом прогоне</t>
   </si>
   <si>
-    <t>Если 2 подряд высоких рейтинга на упражнении — откат ОБЯЗАН сработать в следующем цикле</t>
-  </si>
-  <si>
-    <t>в этом прогоне не было 2 подряд высоких рейтингов</t>
+    <t>Откат (one-shot): agg.hardStreak движка совпадает с эталонной реализацией алгоритма на каждом цикле</t>
+  </si>
+  <si>
+    <t>все 49 проверенных цикла(ов) совпадают с эталоном</t>
   </si>
   <si>
     <t>Проценты роста только из таблицы методики {10,7,5,3,2}</t>
@@ -442,196 +450,34 @@
     <t>все веса в разумных пределах</t>
   </si>
   <si>
-    <t>12 срабатываний, все — после 2 тяжёлых подряд</t>
-  </si>
-  <si>
-    <t>12 срабатываний: Приседания (цикл 3): предыдущие 2 оценки [4,4]; Румынская стоя на одной ноге с отведением второй ноги назад (цикл 3): предыдущие 2 оценки [4,4]; Приседания (цикл 4): предыдущие 2 оценки [4,4]; Румынская стоя на одной ноге с отведением второй ноги назад (цикл 4): предыдущие 2 оценки [4,4]; Приседания (цикл 5): предыдущие 2 оценки [4,4]; Румынская стоя на одной ноге с отведением второй ноги назад (цикл 5): предыдущие 2 оценки [4,4]; Приседания (цикл 6): предыдущие 2 оценки [4,4]; Румынская стоя на одной ноге с отведением второй ноги назад (цикл 6): предыдущие 2 оценки [4,4]; Приседания (цикл 7): предыдущие 2 оценки [4,4]; Румынская стоя на одной ноге с отведением второй ноги назад (цикл 7): предыдущие 2 оценки [4,4]; Приседания (цикл 8): предыдущие 2 оценки [4,4]; Румынская стоя на одной ноге с отведением второй ноги назад (цикл 8): предыдущие 2 оценки [4,4]</t>
-  </si>
-  <si>
-    <t>все 12 случай(ев) вызвали откат</t>
+    <t>6 срабатываний, все — после 2 тяжёлых подряд</t>
+  </si>
+  <si>
+    <t>6 срабатываний: Приседания (цикл 3): предыдущие 2 оценки [4,4]; Румынская стоя на одной ноге с отведением второй ноги назад (цикл 3): предыдущие 2 оценки [4,4]; Приседания (цикл 5): предыдущие 2 оценки [4,4]; Румынская стоя на одной ноге с отведением второй ноги назад (цикл 5): предыдущие 2 оценки [4,4]; Приседания (цикл 7): предыдущие 2 оценки [4,4]; Румынская стоя на одной ноге с отведением второй ноги назад (цикл 7): предыдущие 2 оценки [4,4]</t>
+  </si>
+  <si>
+    <t>все 42 проверенных цикла(ов) совпадают с эталоном</t>
   </si>
   <si>
     <t>2 срабатываний, все — после 2 тяжёлых подряд</t>
   </si>
   <si>
-    <t>2 срабатываний: Приседания (цикл 3): предыдущие 2 оценки [4,5]; Приседания (цикл 4): предыдущие 2 оценки [5,4]</t>
-  </si>
-  <si>
-    <t>все 2 случай(ев) вызвали откат</t>
+    <t>2 срабатываний: Приседания (цикл 3): предыдущие 2 оценки [4,5]; Приседания (цикл 7): предыдущие 2 оценки [4,5]</t>
+  </si>
+  <si>
+    <t>Откат (one-shot) на Наталье: разовое срабатывание не повторяется немедленно, но срабатывает снова позже на новой паре</t>
+  </si>
+  <si>
+    <t>минимум 1 случай "тяжёлая сразу после отката не вызвала повтор" И минимум 2 срабатывания отката за 8 циклов</t>
+  </si>
+  <si>
+    <t>срабатываний всего: 2; суппрессия сразу после отката: да</t>
   </si>
   <si>
     <t>У новичка без инвентаря нет упражнений со штангой/весом</t>
   </si>
   <si>
     <t>ни одного подхода с весом в кг</t>
-  </si>
-  <si>
-    <t>Назначение</t>
-  </si>
-  <si>
-    <t>Сессия</t>
-  </si>
-  <si>
-    <t>Дата</t>
-  </si>
-  <si>
-    <t>Стартовый замер?</t>
-  </si>
-  <si>
-    <t>Рекомендация (кг)</t>
-  </si>
-  <si>
-    <t>Записано (кг×повт)</t>
-  </si>
-  <si>
-    <t>Оценка усилия</t>
-  </si>
-  <si>
-    <t>Откат?</t>
-  </si>
-  <si>
-    <t>% роста применён</t>
-  </si>
-  <si>
-    <t>Обычная прогрессия (контроль)</t>
-  </si>
-  <si>
-    <t>2026-07-08</t>
-  </si>
-  <si>
-    <t>Да (без рекомендации)</t>
-  </si>
-  <si>
-    <t>—</t>
-  </si>
-  <si>
-    <t>10кг×15</t>
-  </si>
-  <si>
-    <t>2026-07-11</t>
-  </si>
-  <si>
-    <t>2026-07-14</t>
-  </si>
-  <si>
-    <t>2026-07-17</t>
-  </si>
-  <si>
-    <t>2026-07-20</t>
-  </si>
-  <si>
-    <t>2026-07-23</t>
-  </si>
-  <si>
-    <t>2026-07-26</t>
-  </si>
-  <si>
-    <t>2026-07-29</t>
-  </si>
-  <si>
-    <t>20кг×12</t>
-  </si>
-  <si>
-    <t>22.5кг×12</t>
-  </si>
-  <si>
-    <t>25кг×12</t>
-  </si>
-  <si>
-    <t>27.5кг×12</t>
-  </si>
-  <si>
-    <t>30кг×12</t>
-  </si>
-  <si>
-    <t>32.5кг×12</t>
-  </si>
-  <si>
-    <t>Откат: 2 подряд тяжёлых оценки</t>
-  </si>
-  <si>
-    <t>40кг×12</t>
-  </si>
-  <si>
-    <t>42.5кг×12</t>
-  </si>
-  <si>
-    <t>45кг×12</t>
-  </si>
-  <si>
-    <t>47.5кг×12</t>
-  </si>
-  <si>
-    <t>50кг×12</t>
-  </si>
-  <si>
-    <t>Ассистирующий тренажёр (гравитрон) → к нулю</t>
-  </si>
-  <si>
-    <t>-39кг×12</t>
-  </si>
-  <si>
-    <t>-37.5кг×12</t>
-  </si>
-  <si>
-    <t>-35кг×12</t>
-  </si>
-  <si>
-    <t>-32.5кг×12</t>
-  </si>
-  <si>
-    <t>-30кг×12</t>
-  </si>
-  <si>
-    <t>-27.5кг×12</t>
-  </si>
-  <si>
-    <t>-25кг×12</t>
-  </si>
-  <si>
-    <t>-22.5кг×12</t>
-  </si>
-  <si>
-    <t>Проверка "вес привязан к exercise_id, а не к тексту": Марина-A и Марина-B — два отдельных упражнения с ОДИНАКОВЫМ названием ("ТЕСТ-ФЛОУ: Жим гантелей (дубль по названию)"), разные exercise_id. Ветка A (лёгкие оценки, рост): 8 подходов в БД, кг сессии 8 = 60, откаты по сессиям = [false,false,false,false,false,false,false,false]. Ветка B (тяжёлые оценки, откат): 8 подходов в БД, кг сессии 8 = 40, откаты по сессиям = [false,false,true,true,true,true,true,true]. Истории физически изолированы и разошлись — вес считается по id, не по названию.</t>
-  </si>
-  <si>
-    <t>Тест-кейсы флоу Конструктора</t>
-  </si>
-  <si>
-    <t>Рекомендация появляется начиная со 2-й сессии, не на 1-й</t>
-  </si>
-  <si>
-    <t>сессия 1 без рекомендации (стартовый замер), сессии 2-8 с рекомендацией</t>
-  </si>
-  <si>
-    <t>Вес привязан к exercise_id, а не к тексту (два упражнения с одинаковым названием)</t>
-  </si>
-  <si>
-    <t>Марина (A/B)</t>
-  </si>
-  <si>
-    <t>изоляция в БД: по 8 подходов на каждый id; траектории (вес и/или паттерн отката) разошлись</t>
-  </si>
-  <si>
-    <t>id A: 8 подходов, кг сессии 8=60, откаты=[false,false,false,false,false,false,false,false]; id B: 8 подходов, кг сессии 8=40, откаты=[false,false,true,true,true,true,true,true]</t>
-  </si>
-  <si>
-    <t>Откат срабатывает после 2 подряд тяжёлых оценок (флаг isDeload + вес не растёт)</t>
-  </si>
-  <si>
-    <t>откат сработал минимум раз, appliedPct=0, вес на откате ≤ веса предыдущей сессии</t>
-  </si>
-  <si>
-    <t>откат на сессии: 3, 4; вес не растёт (корректно)</t>
-  </si>
-  <si>
-    <t>Ассистирующий тренажёр (гравитрон): вес движется к нулю без откатов</t>
-  </si>
-  <si>
-    <t>кг монотонно растёт (приближается к 0) на всех сессиях 2-8, откатов нет</t>
-  </si>
-  <si>
-    <t>траектория кг: -39 → -37.5 → -35 → -32.5 → -30 → -27.5 → -25 → -22.5</t>
   </si>
   <si>
     <t>Название A</t>
@@ -789,7 +635,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -810,7 +656,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1290,13 +1135,13 @@
         <v>4480</v>
       </c>
       <c r="E3">
-        <v>5500</v>
+        <v>5350</v>
       </c>
       <c r="F3">
-        <v>22.8</v>
+        <v>19.4</v>
       </c>
       <c r="G3">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="H3">
         <v>3</v>
@@ -1342,10 +1187,10 @@
         <v>6785</v>
       </c>
       <c r="E5">
-        <v>10010</v>
+        <v>9283</v>
       </c>
       <c r="F5">
-        <v>47.5</v>
+        <v>36.8</v>
       </c>
       <c r="G5">
         <v>2</v>
@@ -1529,43 +1374,43 @@
         <v>4600</v>
       </c>
       <c r="D3">
+        <v>4600</v>
+      </c>
+      <c r="E3">
         <v>4750</v>
       </c>
-      <c r="E3">
+      <c r="F3">
         <v>4900</v>
       </c>
-      <c r="F3">
+      <c r="G3">
         <v>5050</v>
       </c>
-      <c r="G3">
+      <c r="H3">
         <v>5200</v>
       </c>
-      <c r="H3">
+      <c r="I3">
         <v>5350</v>
-      </c>
-      <c r="I3">
-        <v>5500</v>
       </c>
       <c r="J3">
         <v>2.7</v>
       </c>
       <c r="K3">
+        <v>0</v>
+      </c>
+      <c r="L3">
         <v>3.3</v>
       </c>
-      <c r="L3">
+      <c r="M3">
         <v>3.2</v>
       </c>
-      <c r="M3">
+      <c r="N3">
         <v>3.1</v>
       </c>
-      <c r="N3">
-        <v>3</v>
-      </c>
       <c r="O3">
+        <v>3</v>
+      </c>
+      <c r="P3">
         <v>2.9</v>
-      </c>
-      <c r="P3">
-        <v>2.8</v>
       </c>
     </row>
     <row r="4" spans="1:16" x14ac:dyDescent="0.25">
@@ -1629,43 +1474,43 @@
         <v>7363</v>
       </c>
       <c r="D5">
-        <v>7688</v>
+        <v>7560</v>
       </c>
       <c r="E5">
-        <v>8050</v>
+        <v>7960</v>
       </c>
       <c r="F5">
-        <v>8540</v>
+        <v>8323</v>
       </c>
       <c r="G5">
-        <v>9030</v>
+        <v>8685</v>
       </c>
       <c r="H5">
-        <v>9520</v>
+        <v>8883</v>
       </c>
       <c r="I5">
-        <v>10010</v>
+        <v>9283</v>
       </c>
       <c r="J5">
         <v>8.5</v>
       </c>
       <c r="K5">
+        <v>2.7</v>
+      </c>
+      <c r="L5">
+        <v>5.3</v>
+      </c>
+      <c r="M5">
+        <v>4.6</v>
+      </c>
+      <c r="N5">
         <v>4.4</v>
       </c>
-      <c r="L5">
-        <v>4.7</v>
-      </c>
-      <c r="M5">
-        <v>6.1</v>
-      </c>
-      <c r="N5">
-        <v>5.7</v>
-      </c>
       <c r="O5">
-        <v>5.4</v>
+        <v>2.3</v>
       </c>
       <c r="P5">
-        <v>5.1</v>
+        <v>4.5</v>
       </c>
     </row>
     <row r="6" spans="1:16" x14ac:dyDescent="0.25">
@@ -3284,23 +3129,23 @@
       </c>
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A76" s="9" t="s">
+      <c r="A76" t="s">
         <v>11</v>
       </c>
-      <c r="B76" s="9">
+      <c r="B76">
         <v>4</v>
       </c>
-      <c r="C76" s="9" t="s">
+      <c r="C76" t="s">
         <v>44</v>
       </c>
-      <c r="D76" s="9">
+      <c r="D76">
         <v>4</v>
       </c>
-      <c r="E76" s="9" t="s">
-        <v>58</v>
-      </c>
-      <c r="F76" s="9" t="s">
-        <v>59</v>
+      <c r="E76" t="s">
+        <v>45</v>
+      </c>
+      <c r="F76" t="s">
+        <v>46</v>
       </c>
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.25">
@@ -3344,23 +3189,23 @@
       </c>
     </row>
     <row r="79" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A79" s="9" t="s">
+      <c r="A79" t="s">
         <v>11</v>
       </c>
-      <c r="B79" s="9">
+      <c r="B79">
         <v>4</v>
       </c>
-      <c r="C79" s="9" t="s">
+      <c r="C79" t="s">
         <v>55</v>
       </c>
-      <c r="D79" s="9">
+      <c r="D79">
         <v>4</v>
       </c>
-      <c r="E79" s="9" t="s">
-        <v>58</v>
-      </c>
-      <c r="F79" s="9" t="s">
-        <v>59</v>
+      <c r="E79" t="s">
+        <v>45</v>
+      </c>
+      <c r="F79" t="s">
+        <v>46</v>
       </c>
     </row>
     <row r="80" spans="1:6" x14ac:dyDescent="0.25">
@@ -3524,23 +3369,23 @@
       </c>
     </row>
     <row r="88" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A88" s="9" t="s">
+      <c r="A88" t="s">
         <v>11</v>
       </c>
-      <c r="B88" s="9">
+      <c r="B88">
         <v>6</v>
       </c>
-      <c r="C88" s="9" t="s">
+      <c r="C88" t="s">
         <v>44</v>
       </c>
-      <c r="D88" s="9">
+      <c r="D88">
         <v>4</v>
       </c>
-      <c r="E88" s="9" t="s">
-        <v>58</v>
-      </c>
-      <c r="F88" s="9" t="s">
-        <v>59</v>
+      <c r="E88" t="s">
+        <v>45</v>
+      </c>
+      <c r="F88" t="s">
+        <v>46</v>
       </c>
     </row>
     <row r="89" spans="1:6" x14ac:dyDescent="0.25">
@@ -3584,23 +3429,23 @@
       </c>
     </row>
     <row r="91" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A91" s="9" t="s">
+      <c r="A91" t="s">
         <v>11</v>
       </c>
-      <c r="B91" s="9">
+      <c r="B91">
         <v>6</v>
       </c>
-      <c r="C91" s="9" t="s">
+      <c r="C91" t="s">
         <v>55</v>
       </c>
-      <c r="D91" s="9">
+      <c r="D91">
         <v>4</v>
       </c>
-      <c r="E91" s="9" t="s">
-        <v>58</v>
-      </c>
-      <c r="F91" s="9" t="s">
-        <v>59</v>
+      <c r="E91" t="s">
+        <v>45</v>
+      </c>
+      <c r="F91" t="s">
+        <v>46</v>
       </c>
     </row>
     <row r="92" spans="1:6" x14ac:dyDescent="0.25">
@@ -3764,23 +3609,23 @@
       </c>
     </row>
     <row r="100" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A100" s="9" t="s">
+      <c r="A100" t="s">
         <v>11</v>
       </c>
-      <c r="B100" s="9">
-        <v>8</v>
-      </c>
-      <c r="C100" s="9" t="s">
+      <c r="B100">
+        <v>8</v>
+      </c>
+      <c r="C100" t="s">
         <v>44</v>
       </c>
-      <c r="D100" s="9">
+      <c r="D100">
         <v>4</v>
       </c>
-      <c r="E100" s="9" t="s">
-        <v>58</v>
-      </c>
-      <c r="F100" s="9" t="s">
-        <v>59</v>
+      <c r="E100" t="s">
+        <v>45</v>
+      </c>
+      <c r="F100" t="s">
+        <v>46</v>
       </c>
     </row>
     <row r="101" spans="1:6" x14ac:dyDescent="0.25">
@@ -3824,23 +3669,23 @@
       </c>
     </row>
     <row r="103" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A103" s="9" t="s">
+      <c r="A103" t="s">
         <v>11</v>
       </c>
-      <c r="B103" s="9">
-        <v>8</v>
-      </c>
-      <c r="C103" s="9" t="s">
+      <c r="B103">
+        <v>8</v>
+      </c>
+      <c r="C103" t="s">
         <v>55</v>
       </c>
-      <c r="D103" s="9">
+      <c r="D103">
         <v>4</v>
       </c>
-      <c r="E103" s="9" t="s">
-        <v>58</v>
-      </c>
-      <c r="F103" s="9" t="s">
-        <v>59</v>
+      <c r="E103" t="s">
+        <v>45</v>
+      </c>
+      <c r="F103" t="s">
+        <v>46</v>
       </c>
     </row>
     <row r="104" spans="1:6" x14ac:dyDescent="0.25">
@@ -5424,23 +5269,23 @@
       </c>
     </row>
     <row r="183" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A183" s="9" t="s">
+      <c r="A183" t="s">
         <v>17</v>
       </c>
-      <c r="B183" s="9">
+      <c r="B183">
         <v>4</v>
       </c>
-      <c r="C183" s="9" t="s">
+      <c r="C183" t="s">
         <v>44</v>
       </c>
-      <c r="D183" s="9">
-        <v>3</v>
-      </c>
-      <c r="E183" s="9" t="s">
-        <v>58</v>
-      </c>
-      <c r="F183" s="9" t="s">
-        <v>59</v>
+      <c r="D183">
+        <v>3</v>
+      </c>
+      <c r="E183" t="s">
+        <v>45</v>
+      </c>
+      <c r="F183" t="s">
+        <v>46</v>
       </c>
     </row>
     <row r="184" spans="1:6" x14ac:dyDescent="0.25">
@@ -5574,7 +5419,7 @@
         <v>44</v>
       </c>
       <c r="D190">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E190" t="s">
         <v>45</v>
@@ -5714,7 +5559,7 @@
         <v>44</v>
       </c>
       <c r="D197">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E197" t="s">
         <v>45</v>
@@ -5844,23 +5689,23 @@
       </c>
     </row>
     <row r="204" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A204" t="s">
+      <c r="A204" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="B204">
+      <c r="B204" s="9">
         <v>7</v>
       </c>
-      <c r="C204" t="s">
+      <c r="C204" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="D204">
-        <v>3</v>
-      </c>
-      <c r="E204" t="s">
-        <v>45</v>
-      </c>
-      <c r="F204" t="s">
-        <v>46</v>
+      <c r="D204" s="9">
+        <v>3</v>
+      </c>
+      <c r="E204" s="9" t="s">
+        <v>58</v>
+      </c>
+      <c r="F204" s="9" t="s">
+        <v>59</v>
       </c>
     </row>
     <row r="205" spans="1:6" x14ac:dyDescent="0.25">
@@ -7529,22 +7374,22 @@
         <v>74</v>
       </c>
       <c r="E9" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="F9" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="G9" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="H9" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="I9" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="J9" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.25">
@@ -7555,28 +7400,28 @@
         <v>53</v>
       </c>
       <c r="C10" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="D10" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="E10" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="F10" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="G10" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H10" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="I10" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="J10" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.25">
@@ -7587,28 +7432,28 @@
         <v>54</v>
       </c>
       <c r="C11" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="D11" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="E11" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="F11" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="G11" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="H11" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="I11" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="J11" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.25">
@@ -7619,28 +7464,28 @@
         <v>55</v>
       </c>
       <c r="C12" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="D12" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="E12" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="F12" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="G12" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="H12" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="I12" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="J12" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.25">
@@ -7651,28 +7496,28 @@
         <v>56</v>
       </c>
       <c r="C13" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="D13" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="E13" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="F13" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="G13" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="H13" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="I13" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="J13" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.25">
@@ -7683,28 +7528,28 @@
         <v>57</v>
       </c>
       <c r="C14" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="D14" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="E14" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="F14" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="G14" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="H14" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="I14" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="J14" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.25">
@@ -7715,28 +7560,28 @@
         <v>44</v>
       </c>
       <c r="C15" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="D15" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="E15" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="F15" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="G15" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="H15" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="I15" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="J15" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.25">
@@ -7747,28 +7592,28 @@
         <v>60</v>
       </c>
       <c r="C16" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D16" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="E16" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="F16" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="G16" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="H16" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="I16" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="J16" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.25">
@@ -7779,28 +7624,28 @@
         <v>61</v>
       </c>
       <c r="C17" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="D17" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="E17" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="F17" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="G17" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="H17" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="I17" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="J17" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
     </row>
     <row r="18" spans="1:10" x14ac:dyDescent="0.25">
@@ -7811,28 +7656,28 @@
         <v>62</v>
       </c>
       <c r="C18" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="D18" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="E18" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="F18" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="G18" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="H18" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="I18" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="J18" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.25">
@@ -7843,28 +7688,28 @@
         <v>63</v>
       </c>
       <c r="C19" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="D19" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="E19" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="F19" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="G19" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="H19" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="I19" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="J19" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.25">
@@ -7875,28 +7720,28 @@
         <v>64</v>
       </c>
       <c r="C20" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="D20" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="E20" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="F20" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="G20" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="H20" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="I20" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="J20" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.25">
@@ -7907,28 +7752,28 @@
         <v>65</v>
       </c>
       <c r="C21" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="D21" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="E21" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="F21" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="G21" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="H21" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="I21" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="J21" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
     </row>
     <row r="22" spans="1:10" x14ac:dyDescent="0.25">
@@ -7939,28 +7784,28 @@
         <v>44</v>
       </c>
       <c r="C22" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="D22" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="E22" t="s">
-        <v>86</v>
+        <v>111</v>
       </c>
       <c r="F22" t="s">
-        <v>86</v>
+        <v>111</v>
       </c>
       <c r="G22" t="s">
-        <v>87</v>
+        <v>111</v>
       </c>
       <c r="H22" t="s">
-        <v>88</v>
+        <v>111</v>
       </c>
       <c r="I22" t="s">
-        <v>89</v>
+        <v>112</v>
       </c>
       <c r="J22" t="s">
-        <v>90</v>
+        <v>112</v>
       </c>
     </row>
     <row r="23" spans="1:10" x14ac:dyDescent="0.25">
@@ -7971,28 +7816,28 @@
         <v>60</v>
       </c>
       <c r="C23" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D23" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="E23" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="F23" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="G23" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="H23" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="I23" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="J23" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
     </row>
     <row r="24" spans="1:10" x14ac:dyDescent="0.25">
@@ -8003,28 +7848,28 @@
         <v>61</v>
       </c>
       <c r="C24" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="D24" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="E24" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="F24" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="G24" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="H24" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="I24" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="J24" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
     </row>
     <row r="25" spans="1:10" x14ac:dyDescent="0.25">
@@ -8035,28 +7880,28 @@
         <v>62</v>
       </c>
       <c r="C25" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="D25" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="E25" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="F25" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="G25" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="H25" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="I25" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="J25" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="26" spans="1:10" x14ac:dyDescent="0.25">
@@ -8067,28 +7912,28 @@
         <v>63</v>
       </c>
       <c r="C26" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="D26" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="E26" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="F26" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="G26" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="H26" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="I26" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="J26" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="27" spans="1:10" x14ac:dyDescent="0.25">
@@ -8099,28 +7944,28 @@
         <v>64</v>
       </c>
       <c r="C27" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="D27" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="E27" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="F27" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="G27" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="H27" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="I27" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="J27" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="28" spans="1:10" x14ac:dyDescent="0.25">
@@ -8131,28 +7976,28 @@
         <v>65</v>
       </c>
       <c r="C28" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="D28" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="E28" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="F28" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="G28" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="H28" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="I28" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="J28" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
     </row>
     <row r="29" spans="1:10" x14ac:dyDescent="0.25">
@@ -8160,31 +8005,31 @@
         <v>18</v>
       </c>
       <c r="B29" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="C29" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="D29" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="E29" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="F29" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="G29" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="H29" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="I29" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="J29" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
     </row>
     <row r="30" spans="1:10" x14ac:dyDescent="0.25">
@@ -8195,28 +8040,28 @@
         <v>62</v>
       </c>
       <c r="C30" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="D30" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="E30" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="F30" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="G30" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="H30" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="I30" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="J30" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
     </row>
     <row r="31" spans="1:10" x14ac:dyDescent="0.25">
@@ -8227,28 +8072,28 @@
         <v>67</v>
       </c>
       <c r="C31" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="D31" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="E31" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="F31" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="G31" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="H31" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="I31" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="J31" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
     </row>
     <row r="32" spans="1:10" x14ac:dyDescent="0.25">
@@ -8259,28 +8104,28 @@
         <v>68</v>
       </c>
       <c r="C32" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="D32" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="E32" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="F32" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="G32" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="H32" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="I32" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="J32" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
     </row>
     <row r="33" spans="1:10" x14ac:dyDescent="0.25">
@@ -8291,28 +8136,28 @@
         <v>69</v>
       </c>
       <c r="C33" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="D33" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="E33" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="F33" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="G33" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="H33" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="I33" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="J33" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="34" spans="1:10" x14ac:dyDescent="0.25">
@@ -8355,28 +8200,28 @@
         <v>65</v>
       </c>
       <c r="C35" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="D35" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="E35" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="F35" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="G35" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="H35" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="I35" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="J35" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
     </row>
   </sheetData>
@@ -8387,7 +8232,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E37"/>
+  <dimension ref="A1:E38"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="45" customWidth="1"/>
@@ -8399,512 +8244,512 @@
   <sheetData>
     <row r="1" ht="24" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="E1" s="10" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="B2" t="s">
         <v>8</v>
       </c>
       <c r="C2" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="D2" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="E2" s="11" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="B3" t="s">
         <v>8</v>
       </c>
       <c r="C3" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="D3" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="E3" s="11" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
+        <v>132</v>
+      </c>
+      <c r="B4" t="s">
+        <v>8</v>
+      </c>
+      <c r="C4" t="s">
+        <v>133</v>
+      </c>
+      <c r="D4" t="s">
+        <v>134</v>
+      </c>
+      <c r="E4" s="11" t="s">
         <v>129</v>
-      </c>
-      <c r="B4" t="s">
-        <v>8</v>
-      </c>
-      <c r="C4" t="s">
-        <v>130</v>
-      </c>
-      <c r="D4" t="s">
-        <v>131</v>
-      </c>
-      <c r="E4" s="11" t="s">
-        <v>126</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="B5" t="s">
         <v>8</v>
       </c>
       <c r="C5" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="D5" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="E5" s="11" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="B6" t="s">
         <v>8</v>
       </c>
       <c r="C6" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="D6" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="E6" s="11" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="B7" t="s">
         <v>8</v>
       </c>
       <c r="C7" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="D7" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="E7" s="11" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="B8" t="s">
         <v>8</v>
       </c>
       <c r="C8" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="D8" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="E8" s="11" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="B9" t="s">
         <v>11</v>
       </c>
       <c r="C9" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="D9" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="E9" s="11" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="B10" t="s">
         <v>11</v>
       </c>
       <c r="C10" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="D10" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="E10" s="11" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="B11" t="s">
         <v>11</v>
       </c>
       <c r="C11" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="D11" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="E11" s="11" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="B12" t="s">
         <v>11</v>
       </c>
       <c r="C12" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="D12" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="E12" s="11" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="B13" t="s">
         <v>11</v>
       </c>
       <c r="C13" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="D13" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="E13" s="11" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="B14" t="s">
         <v>11</v>
       </c>
       <c r="C14" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="D14" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="E14" s="11" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="B15" t="s">
         <v>11</v>
       </c>
       <c r="C15" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="D15" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="E15" s="11" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="B16" t="s">
         <v>14</v>
       </c>
       <c r="C16" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="D16" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="E16" s="11" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="B17" t="s">
         <v>14</v>
       </c>
       <c r="C17" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="D17" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="E17" s="11" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="B18" t="s">
         <v>14</v>
       </c>
       <c r="C18" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="D18" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="E18" s="11" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="B19" t="s">
         <v>14</v>
       </c>
       <c r="C19" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="D19" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="E19" s="11" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="B20" t="s">
         <v>14</v>
       </c>
       <c r="C20" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="D20" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="E20" s="11" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="B21" t="s">
         <v>14</v>
       </c>
       <c r="C21" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="D21" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="E21" s="11" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="B22" t="s">
         <v>14</v>
       </c>
       <c r="C22" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="D22" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="E22" s="11" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="B23" t="s">
         <v>17</v>
       </c>
       <c r="C23" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="D23" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="E23" s="11" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="B24" t="s">
         <v>17</v>
       </c>
       <c r="C24" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="D24" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="E24" s="11" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="B25" t="s">
         <v>17</v>
       </c>
       <c r="C25" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="D25" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="E25" s="11" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="B26" t="s">
         <v>17</v>
       </c>
       <c r="C26" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="D26" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="E26" s="11" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="B27" t="s">
         <v>17</v>
       </c>
       <c r="C27" t="s">
-        <v>146</v>
+        <v>139</v>
       </c>
       <c r="D27" t="s">
-        <v>146</v>
+        <v>139</v>
       </c>
       <c r="E27" s="11" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>137</v>
+        <v>149</v>
       </c>
       <c r="B28" t="s">
         <v>17</v>
       </c>
       <c r="C28" t="s">
-        <v>138</v>
+        <v>150</v>
       </c>
       <c r="D28" t="s">
-        <v>138</v>
+        <v>151</v>
       </c>
       <c r="E28" s="11" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="B29" t="s">
         <v>17</v>
       </c>
       <c r="C29" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="D29" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="E29" s="11" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>124</v>
+        <v>142</v>
       </c>
       <c r="B30" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C30" t="s">
-        <v>125</v>
+        <v>143</v>
       </c>
       <c r="D30" t="s">
-        <v>125</v>
+        <v>143</v>
       </c>
       <c r="E30" s="11" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.25">
@@ -8921,24 +8766,24 @@
         <v>128</v>
       </c>
       <c r="E31" s="11" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="B32" t="s">
         <v>18</v>
       </c>
       <c r="C32" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="D32" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="E32" s="11" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.25">
@@ -8952,10 +8797,10 @@
         <v>133</v>
       </c>
       <c r="D33" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="E33" s="11" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.25">
@@ -8969,61 +8814,78 @@
         <v>136</v>
       </c>
       <c r="D34" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="E34" s="11" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="B35" t="s">
         <v>18</v>
       </c>
       <c r="C35" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="D35" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="E35" s="11" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="B36" t="s">
         <v>18</v>
       </c>
       <c r="C36" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="D36" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="E36" s="11" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>147</v>
+        <v>142</v>
       </c>
       <c r="B37" t="s">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="C37" t="s">
-        <v>148</v>
+        <v>143</v>
       </c>
       <c r="D37" t="s">
-        <v>148</v>
+        <v>143</v>
       </c>
       <c r="E37" s="11" t="s">
-        <v>126</v>
+        <v>129</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
+        <v>152</v>
+      </c>
+      <c r="B38" t="s">
+        <v>8</v>
+      </c>
+      <c r="C38" t="s">
+        <v>153</v>
+      </c>
+      <c r="D38" t="s">
+        <v>153</v>
+      </c>
+      <c r="E38" s="11" t="s">
+        <v>129</v>
       </c>
     </row>
   </sheetData>
@@ -9033,1241 +8895,6 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:J48"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
-  <cols>
-    <col min="1" max="1" width="14" customWidth="1"/>
-    <col min="2" max="2" width="34" customWidth="1"/>
-    <col min="4" max="4" width="12" customWidth="1"/>
-    <col min="5" max="6" width="16" customWidth="1"/>
-    <col min="7" max="7" width="18" customWidth="1"/>
-    <col min="8" max="8" width="14" customWidth="1"/>
-    <col min="9" max="9" width="10" customWidth="1"/>
-    <col min="10" max="10" width="16" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="24" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>149</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>150</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>151</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>152</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>154</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>155</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>156</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>8</v>
-      </c>
-      <c r="B2" t="s">
-        <v>158</v>
-      </c>
-      <c r="C2">
-        <v>1</v>
-      </c>
-      <c r="D2" t="s">
-        <v>159</v>
-      </c>
-      <c r="E2" t="s">
-        <v>160</v>
-      </c>
-      <c r="F2" t="s">
-        <v>161</v>
-      </c>
-      <c r="G2" t="s">
-        <v>162</v>
-      </c>
-      <c r="H2">
-        <v>3</v>
-      </c>
-      <c r="I2" t="s">
-        <v>45</v>
-      </c>
-      <c r="J2" t="s">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>8</v>
-      </c>
-      <c r="B3" t="s">
-        <v>158</v>
-      </c>
-      <c r="C3">
-        <v>2</v>
-      </c>
-      <c r="D3" t="s">
-        <v>163</v>
-      </c>
-      <c r="E3" t="s">
-        <v>45</v>
-      </c>
-      <c r="F3">
-        <v>10</v>
-      </c>
-      <c r="G3" t="s">
-        <v>162</v>
-      </c>
-      <c r="H3">
-        <v>3</v>
-      </c>
-      <c r="I3" t="s">
-        <v>45</v>
-      </c>
-      <c r="J3">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>8</v>
-      </c>
-      <c r="B4" t="s">
-        <v>158</v>
-      </c>
-      <c r="C4">
-        <v>3</v>
-      </c>
-      <c r="D4" t="s">
-        <v>164</v>
-      </c>
-      <c r="E4" t="s">
-        <v>45</v>
-      </c>
-      <c r="F4">
-        <v>10</v>
-      </c>
-      <c r="G4" t="s">
-        <v>162</v>
-      </c>
-      <c r="H4">
-        <v>3</v>
-      </c>
-      <c r="I4" t="s">
-        <v>45</v>
-      </c>
-      <c r="J4">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>8</v>
-      </c>
-      <c r="B5" t="s">
-        <v>158</v>
-      </c>
-      <c r="C5">
-        <v>4</v>
-      </c>
-      <c r="D5" t="s">
-        <v>165</v>
-      </c>
-      <c r="E5" t="s">
-        <v>45</v>
-      </c>
-      <c r="F5">
-        <v>10</v>
-      </c>
-      <c r="G5" t="s">
-        <v>162</v>
-      </c>
-      <c r="H5">
-        <v>3</v>
-      </c>
-      <c r="I5" t="s">
-        <v>45</v>
-      </c>
-      <c r="J5">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>8</v>
-      </c>
-      <c r="B6" t="s">
-        <v>158</v>
-      </c>
-      <c r="C6">
-        <v>5</v>
-      </c>
-      <c r="D6" t="s">
-        <v>166</v>
-      </c>
-      <c r="E6" t="s">
-        <v>45</v>
-      </c>
-      <c r="F6">
-        <v>10</v>
-      </c>
-      <c r="G6" t="s">
-        <v>162</v>
-      </c>
-      <c r="H6">
-        <v>3</v>
-      </c>
-      <c r="I6" t="s">
-        <v>45</v>
-      </c>
-      <c r="J6">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>8</v>
-      </c>
-      <c r="B7" t="s">
-        <v>158</v>
-      </c>
-      <c r="C7">
-        <v>6</v>
-      </c>
-      <c r="D7" t="s">
-        <v>167</v>
-      </c>
-      <c r="E7" t="s">
-        <v>45</v>
-      </c>
-      <c r="F7">
-        <v>10</v>
-      </c>
-      <c r="G7" t="s">
-        <v>162</v>
-      </c>
-      <c r="H7">
-        <v>3</v>
-      </c>
-      <c r="I7" t="s">
-        <v>45</v>
-      </c>
-      <c r="J7">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>8</v>
-      </c>
-      <c r="B8" t="s">
-        <v>158</v>
-      </c>
-      <c r="C8">
-        <v>7</v>
-      </c>
-      <c r="D8" t="s">
-        <v>168</v>
-      </c>
-      <c r="E8" t="s">
-        <v>45</v>
-      </c>
-      <c r="F8">
-        <v>10</v>
-      </c>
-      <c r="G8" t="s">
-        <v>162</v>
-      </c>
-      <c r="H8">
-        <v>3</v>
-      </c>
-      <c r="I8" t="s">
-        <v>45</v>
-      </c>
-      <c r="J8">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>8</v>
-      </c>
-      <c r="B9" t="s">
-        <v>158</v>
-      </c>
-      <c r="C9">
-        <v>8</v>
-      </c>
-      <c r="D9" t="s">
-        <v>169</v>
-      </c>
-      <c r="E9" t="s">
-        <v>45</v>
-      </c>
-      <c r="F9">
-        <v>10</v>
-      </c>
-      <c r="G9" t="s">
-        <v>162</v>
-      </c>
-      <c r="H9">
-        <v>3</v>
-      </c>
-      <c r="I9" t="s">
-        <v>45</v>
-      </c>
-      <c r="J9">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
-        <v>14</v>
-      </c>
-      <c r="B11" t="s">
-        <v>158</v>
-      </c>
-      <c r="C11">
-        <v>1</v>
-      </c>
-      <c r="D11" t="s">
-        <v>159</v>
-      </c>
-      <c r="E11" t="s">
-        <v>160</v>
-      </c>
-      <c r="F11" t="s">
-        <v>161</v>
-      </c>
-      <c r="G11" t="s">
-        <v>170</v>
-      </c>
-      <c r="H11">
-        <v>3</v>
-      </c>
-      <c r="I11" t="s">
-        <v>45</v>
-      </c>
-      <c r="J11" t="s">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
-        <v>14</v>
-      </c>
-      <c r="B12" t="s">
-        <v>158</v>
-      </c>
-      <c r="C12">
-        <v>2</v>
-      </c>
-      <c r="D12" t="s">
-        <v>163</v>
-      </c>
-      <c r="E12" t="s">
-        <v>45</v>
-      </c>
-      <c r="F12">
-        <v>20</v>
-      </c>
-      <c r="G12" t="s">
-        <v>170</v>
-      </c>
-      <c r="H12">
-        <v>2</v>
-      </c>
-      <c r="I12" t="s">
-        <v>45</v>
-      </c>
-      <c r="J12">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
-        <v>14</v>
-      </c>
-      <c r="B13" t="s">
-        <v>158</v>
-      </c>
-      <c r="C13">
-        <v>3</v>
-      </c>
-      <c r="D13" t="s">
-        <v>164</v>
-      </c>
-      <c r="E13" t="s">
-        <v>45</v>
-      </c>
-      <c r="F13">
-        <v>22.5</v>
-      </c>
-      <c r="G13" t="s">
-        <v>171</v>
-      </c>
-      <c r="H13">
-        <v>3</v>
-      </c>
-      <c r="I13" t="s">
-        <v>45</v>
-      </c>
-      <c r="J13">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
-        <v>14</v>
-      </c>
-      <c r="B14" t="s">
-        <v>158</v>
-      </c>
-      <c r="C14">
-        <v>4</v>
-      </c>
-      <c r="D14" t="s">
-        <v>165</v>
-      </c>
-      <c r="E14" t="s">
-        <v>45</v>
-      </c>
-      <c r="F14">
-        <v>22.5</v>
-      </c>
-      <c r="G14" t="s">
-        <v>171</v>
-      </c>
-      <c r="H14">
-        <v>2</v>
-      </c>
-      <c r="I14" t="s">
-        <v>45</v>
-      </c>
-      <c r="J14">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A15" t="s">
-        <v>14</v>
-      </c>
-      <c r="B15" t="s">
-        <v>158</v>
-      </c>
-      <c r="C15">
-        <v>5</v>
-      </c>
-      <c r="D15" t="s">
-        <v>166</v>
-      </c>
-      <c r="E15" t="s">
-        <v>45</v>
-      </c>
-      <c r="F15">
-        <v>25</v>
-      </c>
-      <c r="G15" t="s">
-        <v>172</v>
-      </c>
-      <c r="H15">
-        <v>3</v>
-      </c>
-      <c r="I15" t="s">
-        <v>45</v>
-      </c>
-      <c r="J15">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A16" t="s">
-        <v>14</v>
-      </c>
-      <c r="B16" t="s">
-        <v>158</v>
-      </c>
-      <c r="C16">
-        <v>6</v>
-      </c>
-      <c r="D16" t="s">
-        <v>167</v>
-      </c>
-      <c r="E16" t="s">
-        <v>45</v>
-      </c>
-      <c r="F16">
-        <v>27.5</v>
-      </c>
-      <c r="G16" t="s">
-        <v>173</v>
-      </c>
-      <c r="H16">
-        <v>2</v>
-      </c>
-      <c r="I16" t="s">
-        <v>45</v>
-      </c>
-      <c r="J16">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A17" t="s">
-        <v>14</v>
-      </c>
-      <c r="B17" t="s">
-        <v>158</v>
-      </c>
-      <c r="C17">
-        <v>7</v>
-      </c>
-      <c r="D17" t="s">
-        <v>168</v>
-      </c>
-      <c r="E17" t="s">
-        <v>45</v>
-      </c>
-      <c r="F17">
-        <v>30</v>
-      </c>
-      <c r="G17" t="s">
-        <v>174</v>
-      </c>
-      <c r="H17">
-        <v>3</v>
-      </c>
-      <c r="I17" t="s">
-        <v>45</v>
-      </c>
-      <c r="J17">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A18" t="s">
-        <v>14</v>
-      </c>
-      <c r="B18" t="s">
-        <v>158</v>
-      </c>
-      <c r="C18">
-        <v>8</v>
-      </c>
-      <c r="D18" t="s">
-        <v>169</v>
-      </c>
-      <c r="E18" t="s">
-        <v>45</v>
-      </c>
-      <c r="F18">
-        <v>32.5</v>
-      </c>
-      <c r="G18" t="s">
-        <v>175</v>
-      </c>
-      <c r="H18">
-        <v>2</v>
-      </c>
-      <c r="I18" t="s">
-        <v>45</v>
-      </c>
-      <c r="J18">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A20" t="s">
-        <v>17</v>
-      </c>
-      <c r="B20" t="s">
-        <v>176</v>
-      </c>
-      <c r="C20">
-        <v>1</v>
-      </c>
-      <c r="D20" t="s">
-        <v>159</v>
-      </c>
-      <c r="E20" t="s">
-        <v>160</v>
-      </c>
-      <c r="F20" t="s">
-        <v>161</v>
-      </c>
-      <c r="G20" t="s">
-        <v>177</v>
-      </c>
-      <c r="H20">
-        <v>4</v>
-      </c>
-      <c r="I20" t="s">
-        <v>45</v>
-      </c>
-      <c r="J20" t="s">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A21" t="s">
-        <v>17</v>
-      </c>
-      <c r="B21" t="s">
-        <v>176</v>
-      </c>
-      <c r="C21">
-        <v>2</v>
-      </c>
-      <c r="D21" t="s">
-        <v>163</v>
-      </c>
-      <c r="E21" t="s">
-        <v>45</v>
-      </c>
-      <c r="F21">
-        <v>40</v>
-      </c>
-      <c r="G21" t="s">
-        <v>177</v>
-      </c>
-      <c r="H21">
-        <v>5</v>
-      </c>
-      <c r="I21" t="s">
-        <v>45</v>
-      </c>
-      <c r="J21">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="22" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A22" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="B22" s="9" t="s">
-        <v>176</v>
-      </c>
-      <c r="C22" s="9">
-        <v>3</v>
-      </c>
-      <c r="D22" s="9" t="s">
-        <v>164</v>
-      </c>
-      <c r="E22" s="9" t="s">
-        <v>45</v>
-      </c>
-      <c r="F22" s="9">
-        <v>40</v>
-      </c>
-      <c r="G22" s="9" t="s">
-        <v>177</v>
-      </c>
-      <c r="H22" s="9">
-        <v>4</v>
-      </c>
-      <c r="I22" s="9" t="s">
-        <v>58</v>
-      </c>
-      <c r="J22" s="9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A23" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="B23" s="9" t="s">
-        <v>176</v>
-      </c>
-      <c r="C23" s="9">
-        <v>4</v>
-      </c>
-      <c r="D23" s="9" t="s">
-        <v>165</v>
-      </c>
-      <c r="E23" s="9" t="s">
-        <v>45</v>
-      </c>
-      <c r="F23" s="9">
-        <v>40</v>
-      </c>
-      <c r="G23" s="9" t="s">
-        <v>177</v>
-      </c>
-      <c r="H23" s="9">
-        <v>3</v>
-      </c>
-      <c r="I23" s="9" t="s">
-        <v>58</v>
-      </c>
-      <c r="J23" s="9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A24" t="s">
-        <v>17</v>
-      </c>
-      <c r="B24" t="s">
-        <v>176</v>
-      </c>
-      <c r="C24">
-        <v>5</v>
-      </c>
-      <c r="D24" t="s">
-        <v>166</v>
-      </c>
-      <c r="E24" t="s">
-        <v>45</v>
-      </c>
-      <c r="F24">
-        <v>42.5</v>
-      </c>
-      <c r="G24" t="s">
-        <v>178</v>
-      </c>
-      <c r="H24">
-        <v>3</v>
-      </c>
-      <c r="I24" t="s">
-        <v>45</v>
-      </c>
-      <c r="J24">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A25" t="s">
-        <v>17</v>
-      </c>
-      <c r="B25" t="s">
-        <v>176</v>
-      </c>
-      <c r="C25">
-        <v>6</v>
-      </c>
-      <c r="D25" t="s">
-        <v>167</v>
-      </c>
-      <c r="E25" t="s">
-        <v>45</v>
-      </c>
-      <c r="F25">
-        <v>45</v>
-      </c>
-      <c r="G25" t="s">
-        <v>179</v>
-      </c>
-      <c r="H25">
-        <v>3</v>
-      </c>
-      <c r="I25" t="s">
-        <v>45</v>
-      </c>
-      <c r="J25">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="26" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A26" t="s">
-        <v>17</v>
-      </c>
-      <c r="B26" t="s">
-        <v>176</v>
-      </c>
-      <c r="C26">
-        <v>7</v>
-      </c>
-      <c r="D26" t="s">
-        <v>168</v>
-      </c>
-      <c r="E26" t="s">
-        <v>45</v>
-      </c>
-      <c r="F26">
-        <v>47.5</v>
-      </c>
-      <c r="G26" t="s">
-        <v>180</v>
-      </c>
-      <c r="H26">
-        <v>3</v>
-      </c>
-      <c r="I26" t="s">
-        <v>45</v>
-      </c>
-      <c r="J26">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="27" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A27" t="s">
-        <v>17</v>
-      </c>
-      <c r="B27" t="s">
-        <v>176</v>
-      </c>
-      <c r="C27">
-        <v>8</v>
-      </c>
-      <c r="D27" t="s">
-        <v>169</v>
-      </c>
-      <c r="E27" t="s">
-        <v>45</v>
-      </c>
-      <c r="F27">
-        <v>50</v>
-      </c>
-      <c r="G27" t="s">
-        <v>181</v>
-      </c>
-      <c r="H27">
-        <v>3</v>
-      </c>
-      <c r="I27" t="s">
-        <v>45</v>
-      </c>
-      <c r="J27">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="29" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A29" t="s">
-        <v>18</v>
-      </c>
-      <c r="B29" t="s">
-        <v>182</v>
-      </c>
-      <c r="C29">
-        <v>1</v>
-      </c>
-      <c r="D29" t="s">
-        <v>159</v>
-      </c>
-      <c r="E29" t="s">
-        <v>160</v>
-      </c>
-      <c r="F29" t="s">
-        <v>161</v>
-      </c>
-      <c r="G29" t="s">
-        <v>183</v>
-      </c>
-      <c r="H29">
-        <v>2</v>
-      </c>
-      <c r="I29" t="s">
-        <v>45</v>
-      </c>
-      <c r="J29" t="s">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="30" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A30" t="s">
-        <v>18</v>
-      </c>
-      <c r="B30" t="s">
-        <v>182</v>
-      </c>
-      <c r="C30">
-        <v>2</v>
-      </c>
-      <c r="D30" t="s">
-        <v>163</v>
-      </c>
-      <c r="E30" t="s">
-        <v>45</v>
-      </c>
-      <c r="F30">
-        <v>-37.5</v>
-      </c>
-      <c r="G30" t="s">
-        <v>184</v>
-      </c>
-      <c r="H30">
-        <v>2</v>
-      </c>
-      <c r="I30" t="s">
-        <v>45</v>
-      </c>
-      <c r="J30">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="31" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A31" t="s">
-        <v>18</v>
-      </c>
-      <c r="B31" t="s">
-        <v>182</v>
-      </c>
-      <c r="C31">
-        <v>3</v>
-      </c>
-      <c r="D31" t="s">
-        <v>164</v>
-      </c>
-      <c r="E31" t="s">
-        <v>45</v>
-      </c>
-      <c r="F31">
-        <v>-35</v>
-      </c>
-      <c r="G31" t="s">
-        <v>185</v>
-      </c>
-      <c r="H31">
-        <v>2</v>
-      </c>
-      <c r="I31" t="s">
-        <v>45</v>
-      </c>
-      <c r="J31">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="32" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A32" t="s">
-        <v>18</v>
-      </c>
-      <c r="B32" t="s">
-        <v>182</v>
-      </c>
-      <c r="C32">
-        <v>4</v>
-      </c>
-      <c r="D32" t="s">
-        <v>165</v>
-      </c>
-      <c r="E32" t="s">
-        <v>45</v>
-      </c>
-      <c r="F32">
-        <v>-32.5</v>
-      </c>
-      <c r="G32" t="s">
-        <v>186</v>
-      </c>
-      <c r="H32">
-        <v>2</v>
-      </c>
-      <c r="I32" t="s">
-        <v>45</v>
-      </c>
-      <c r="J32">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="33" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A33" t="s">
-        <v>18</v>
-      </c>
-      <c r="B33" t="s">
-        <v>182</v>
-      </c>
-      <c r="C33">
-        <v>5</v>
-      </c>
-      <c r="D33" t="s">
-        <v>166</v>
-      </c>
-      <c r="E33" t="s">
-        <v>45</v>
-      </c>
-      <c r="F33">
-        <v>-30</v>
-      </c>
-      <c r="G33" t="s">
-        <v>187</v>
-      </c>
-      <c r="H33">
-        <v>2</v>
-      </c>
-      <c r="I33" t="s">
-        <v>45</v>
-      </c>
-      <c r="J33">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="34" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A34" t="s">
-        <v>18</v>
-      </c>
-      <c r="B34" t="s">
-        <v>182</v>
-      </c>
-      <c r="C34">
-        <v>6</v>
-      </c>
-      <c r="D34" t="s">
-        <v>167</v>
-      </c>
-      <c r="E34" t="s">
-        <v>45</v>
-      </c>
-      <c r="F34">
-        <v>-27.5</v>
-      </c>
-      <c r="G34" t="s">
-        <v>188</v>
-      </c>
-      <c r="H34">
-        <v>2</v>
-      </c>
-      <c r="I34" t="s">
-        <v>45</v>
-      </c>
-      <c r="J34">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="35" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A35" t="s">
-        <v>18</v>
-      </c>
-      <c r="B35" t="s">
-        <v>182</v>
-      </c>
-      <c r="C35">
-        <v>7</v>
-      </c>
-      <c r="D35" t="s">
-        <v>168</v>
-      </c>
-      <c r="E35" t="s">
-        <v>45</v>
-      </c>
-      <c r="F35">
-        <v>-25</v>
-      </c>
-      <c r="G35" t="s">
-        <v>189</v>
-      </c>
-      <c r="H35">
-        <v>2</v>
-      </c>
-      <c r="I35" t="s">
-        <v>45</v>
-      </c>
-      <c r="J35">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="36" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A36" t="s">
-        <v>18</v>
-      </c>
-      <c r="B36" t="s">
-        <v>182</v>
-      </c>
-      <c r="C36">
-        <v>8</v>
-      </c>
-      <c r="D36" t="s">
-        <v>169</v>
-      </c>
-      <c r="E36" t="s">
-        <v>45</v>
-      </c>
-      <c r="F36">
-        <v>-22.5</v>
-      </c>
-      <c r="G36" t="s">
-        <v>190</v>
-      </c>
-      <c r="H36">
-        <v>2</v>
-      </c>
-      <c r="I36" t="s">
-        <v>45</v>
-      </c>
-      <c r="J36">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="38" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A38" s="2" t="s">
-        <v>191</v>
-      </c>
-      <c r="B38" s="2"/>
-      <c r="C38" s="2"/>
-      <c r="D38" s="2"/>
-      <c r="E38" s="2"/>
-      <c r="F38" s="2"/>
-      <c r="G38" s="2"/>
-      <c r="H38" s="2"/>
-      <c r="I38" s="2"/>
-      <c r="J38" s="2"/>
-    </row>
-    <row r="40" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A40" s="12" t="s">
-        <v>192</v>
-      </c>
-    </row>
-    <row r="41" ht="24" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A41" s="1" t="s">
-        <v>120</v>
-      </c>
-      <c r="B41" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C41" s="1" t="s">
-        <v>121</v>
-      </c>
-      <c r="D41" s="1" t="s">
-        <v>122</v>
-      </c>
-      <c r="E41" s="1" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A42" t="s">
-        <v>193</v>
-      </c>
-      <c r="B42" t="s">
-        <v>8</v>
-      </c>
-      <c r="C42" t="s">
-        <v>194</v>
-      </c>
-      <c r="D42" t="s">
-        <v>194</v>
-      </c>
-      <c r="E42" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A43" t="s">
-        <v>193</v>
-      </c>
-      <c r="B43" t="s">
-        <v>14</v>
-      </c>
-      <c r="C43" t="s">
-        <v>194</v>
-      </c>
-      <c r="D43" t="s">
-        <v>194</v>
-      </c>
-      <c r="E43" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A44" t="s">
-        <v>193</v>
-      </c>
-      <c r="B44" t="s">
-        <v>17</v>
-      </c>
-      <c r="C44" t="s">
-        <v>194</v>
-      </c>
-      <c r="D44" t="s">
-        <v>194</v>
-      </c>
-      <c r="E44" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A45" t="s">
-        <v>193</v>
-      </c>
-      <c r="B45" t="s">
-        <v>18</v>
-      </c>
-      <c r="C45" t="s">
-        <v>194</v>
-      </c>
-      <c r="D45" t="s">
-        <v>194</v>
-      </c>
-      <c r="E45" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A46" t="s">
-        <v>195</v>
-      </c>
-      <c r="B46" t="s">
-        <v>196</v>
-      </c>
-      <c r="C46" t="s">
-        <v>197</v>
-      </c>
-      <c r="D46" t="s">
-        <v>198</v>
-      </c>
-      <c r="E46" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="47" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A47" t="s">
-        <v>199</v>
-      </c>
-      <c r="B47" t="s">
-        <v>17</v>
-      </c>
-      <c r="C47" t="s">
-        <v>200</v>
-      </c>
-      <c r="D47" t="s">
-        <v>201</v>
-      </c>
-      <c r="E47" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="48" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A48" t="s">
-        <v>202</v>
-      </c>
-      <c r="B48" t="s">
-        <v>18</v>
-      </c>
-      <c r="C48" t="s">
-        <v>203</v>
-      </c>
-      <c r="D48" t="s">
-        <v>204</v>
-      </c>
-      <c r="E48" t="s">
-        <v>126</v>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A38:J38"/>
-  </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:F8"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
@@ -10280,82 +8907,82 @@
   <sheetData>
     <row r="1" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>205</v>
+        <v>154</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>206</v>
+        <v>155</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>207</v>
+        <v>156</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="F1" s="10" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>208</v>
+        <v>157</v>
       </c>
       <c r="B2" t="s">
-        <v>209</v>
+        <v>158</v>
       </c>
       <c r="C2" t="s">
-        <v>210</v>
+        <v>159</v>
       </c>
       <c r="D2" t="s">
-        <v>211</v>
+        <v>160</v>
       </c>
       <c r="E2" t="s">
-        <v>211</v>
+        <v>160</v>
       </c>
       <c r="F2" s="11" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>212</v>
+        <v>161</v>
       </c>
       <c r="B3" t="s">
-        <v>213</v>
+        <v>162</v>
       </c>
       <c r="C3" t="s">
-        <v>214</v>
+        <v>163</v>
       </c>
       <c r="D3" t="s">
-        <v>211</v>
+        <v>160</v>
       </c>
       <c r="E3" t="s">
-        <v>211</v>
+        <v>160</v>
       </c>
       <c r="F3" s="11" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>215</v>
+        <v>164</v>
       </c>
       <c r="B4" t="s">
-        <v>216</v>
+        <v>165</v>
       </c>
       <c r="C4" t="s">
-        <v>217</v>
+        <v>166</v>
       </c>
       <c r="D4" t="s">
-        <v>211</v>
+        <v>160</v>
       </c>
       <c r="E4" t="s">
-        <v>211</v>
+        <v>160</v>
       </c>
       <c r="F4" s="11" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
@@ -10363,79 +8990,79 @@
         <v>44</v>
       </c>
       <c r="B5" t="s">
-        <v>218</v>
+        <v>167</v>
       </c>
       <c r="C5" t="s">
-        <v>219</v>
+        <v>168</v>
       </c>
       <c r="D5" t="s">
-        <v>211</v>
+        <v>160</v>
       </c>
       <c r="E5" t="s">
-        <v>211</v>
+        <v>160</v>
       </c>
       <c r="F5" s="11" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>220</v>
+        <v>169</v>
       </c>
       <c r="B6" t="s">
-        <v>221</v>
+        <v>170</v>
       </c>
       <c r="C6" t="s">
-        <v>222</v>
+        <v>171</v>
       </c>
       <c r="D6" t="s">
-        <v>223</v>
+        <v>172</v>
       </c>
       <c r="E6" t="s">
-        <v>223</v>
+        <v>172</v>
       </c>
       <c r="F6" s="11" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>224</v>
+        <v>173</v>
       </c>
       <c r="B7" t="s">
-        <v>225</v>
+        <v>174</v>
       </c>
       <c r="C7" t="s">
-        <v>226</v>
+        <v>175</v>
       </c>
       <c r="D7" t="s">
-        <v>223</v>
+        <v>172</v>
       </c>
       <c r="E7" t="s">
-        <v>223</v>
+        <v>172</v>
       </c>
       <c r="F7" s="11" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>227</v>
+        <v>176</v>
       </c>
       <c r="B8" t="s">
-        <v>228</v>
+        <v>177</v>
       </c>
       <c r="C8" t="s">
-        <v>229</v>
+        <v>178</v>
       </c>
       <c r="D8" t="s">
-        <v>223</v>
+        <v>172</v>
       </c>
       <c r="E8" t="s">
-        <v>223</v>
+        <v>172</v>
       </c>
       <c r="F8" s="11" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
     </row>
   </sheetData>

--- a/reports/progression-report.xlsx
+++ b/reports/progression-report.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1734" uniqueCount="179">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1774" uniqueCount="198">
   <si>
     <t>Персона</t>
   </si>
@@ -165,13 +165,13 @@
     <t>Ягодичный мост на одной ноге (упор на стул/диван)</t>
   </si>
   <si>
-    <t>Тяга резины 1 лежа на полу</t>
+    <t>Тяга резины лежа на полу</t>
   </si>
   <si>
     <t>Отжимания от пола</t>
   </si>
   <si>
-    <t>Отведение руки с резиной 1</t>
+    <t>Отведение руки с резиной</t>
   </si>
   <si>
     <t>Скручивания лежа на полу</t>
@@ -478,6 +478,63 @@
   </si>
   <si>
     <t>ни одного подхода с весом в кг</t>
+  </si>
+  <si>
+    <t>Каждое упражнение из PROGRAMS_MAP есть в библиотеке EXERCISES (EXERCISE_TYPE)</t>
+  </si>
+  <si>
+    <t>—</t>
+  </si>
+  <si>
+    <t>все названия из шаблонов программ совпадают с библиотекой</t>
+  </si>
+  <si>
+    <t>Холодный старт: нет истории → уровень и повторы берутся из шаблона как есть</t>
+  </si>
+  <si>
+    <t>— (домашняя программа)</t>
+  </si>
+  <si>
+    <t>bandLevel=2, reps=15 (steps=0)</t>
+  </si>
+  <si>
+    <t>5 лёгких тренировок подряд (рейтинг 2) → уровень +1, повторы возвращаются к базовому шаблону</t>
+  </si>
+  <si>
+    <t>steps=5, bandLevel=3, reps=15</t>
+  </si>
+  <si>
+    <t>Лесенка "1/2/3 рез." при steps=5 → каждый подход поднимается на 1 уровень (2/3/4)</t>
+  </si>
+  <si>
+    <t>2/3/4</t>
+  </si>
+  <si>
+    <t>Две тяжёлые тренировки подряд → steps -2 (откат); третья тяжёлая подряд откат НЕ повторяет</t>
+  </si>
+  <si>
+    <t>steps после 4-й тренировки=3, после 5-й=1 (откат), после 6-й=1 (без повторного отката)</t>
+  </si>
+  <si>
+    <t>steps по тренировкам: 1, 2, 3, 3, 1, 1</t>
+  </si>
+  <si>
+    <t>Уровень резины уже 5 + steps толкают на подъём уровня → уровень остаётся 5, надбавка уходит в повторения</t>
+  </si>
+  <si>
+    <t>bandLevel=5, reps=25</t>
+  </si>
+  <si>
+    <t>Упражнение с весом тела (Отжимания) → уровня нет, растут только повторения</t>
+  </si>
+  <si>
+    <t>bandLevel=null, steps=3, reps=18</t>
+  </si>
+  <si>
+    <t>Каждое упражнение из HOME_PROGRAM есть в библиотеке EXERCISES</t>
+  </si>
+  <si>
+    <t>все названия совпадают с библиотекой</t>
   </si>
   <si>
     <t>Название A</t>
@@ -8232,7 +8289,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E38"/>
+  <dimension ref="A1:E46"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="45" customWidth="1"/>
@@ -8885,6 +8942,142 @@
         <v>153</v>
       </c>
       <c r="E38" s="11" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>154</v>
+      </c>
+      <c r="B39" t="s">
+        <v>155</v>
+      </c>
+      <c r="C39" t="s">
+        <v>156</v>
+      </c>
+      <c r="D39" t="s">
+        <v>156</v>
+      </c>
+      <c r="E39" s="11" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
+        <v>157</v>
+      </c>
+      <c r="B40" t="s">
+        <v>158</v>
+      </c>
+      <c r="C40" t="s">
+        <v>159</v>
+      </c>
+      <c r="D40" t="s">
+        <v>159</v>
+      </c>
+      <c r="E40" s="11" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
+        <v>160</v>
+      </c>
+      <c r="B41" t="s">
+        <v>158</v>
+      </c>
+      <c r="C41" t="s">
+        <v>161</v>
+      </c>
+      <c r="D41" t="s">
+        <v>161</v>
+      </c>
+      <c r="E41" s="11" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
+        <v>162</v>
+      </c>
+      <c r="B42" t="s">
+        <v>158</v>
+      </c>
+      <c r="C42" t="s">
+        <v>163</v>
+      </c>
+      <c r="D42" t="s">
+        <v>163</v>
+      </c>
+      <c r="E42" s="11" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
+        <v>164</v>
+      </c>
+      <c r="B43" t="s">
+        <v>158</v>
+      </c>
+      <c r="C43" t="s">
+        <v>165</v>
+      </c>
+      <c r="D43" t="s">
+        <v>166</v>
+      </c>
+      <c r="E43" s="11" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A44" t="s">
+        <v>167</v>
+      </c>
+      <c r="B44" t="s">
+        <v>158</v>
+      </c>
+      <c r="C44" t="s">
+        <v>168</v>
+      </c>
+      <c r="D44" t="s">
+        <v>168</v>
+      </c>
+      <c r="E44" s="11" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A45" t="s">
+        <v>169</v>
+      </c>
+      <c r="B45" t="s">
+        <v>158</v>
+      </c>
+      <c r="C45" t="s">
+        <v>170</v>
+      </c>
+      <c r="D45" t="s">
+        <v>170</v>
+      </c>
+      <c r="E45" s="11" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A46" t="s">
+        <v>171</v>
+      </c>
+      <c r="B46" t="s">
+        <v>158</v>
+      </c>
+      <c r="C46" t="s">
+        <v>172</v>
+      </c>
+      <c r="D46" t="s">
+        <v>172</v>
+      </c>
+      <c r="E46" s="11" t="s">
         <v>129</v>
       </c>
     </row>
@@ -8907,13 +9100,13 @@
   <sheetData>
     <row r="1" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>154</v>
+        <v>173</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>155</v>
+        <v>174</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>156</v>
+        <v>175</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>124</v>
@@ -8927,19 +9120,19 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>157</v>
+        <v>176</v>
       </c>
       <c r="B2" t="s">
-        <v>158</v>
+        <v>177</v>
       </c>
       <c r="C2" t="s">
-        <v>159</v>
+        <v>178</v>
       </c>
       <c r="D2" t="s">
-        <v>160</v>
+        <v>179</v>
       </c>
       <c r="E2" t="s">
-        <v>160</v>
+        <v>179</v>
       </c>
       <c r="F2" s="11" t="s">
         <v>129</v>
@@ -8947,19 +9140,19 @@
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>161</v>
+        <v>180</v>
       </c>
       <c r="B3" t="s">
-        <v>162</v>
+        <v>181</v>
       </c>
       <c r="C3" t="s">
-        <v>163</v>
+        <v>182</v>
       </c>
       <c r="D3" t="s">
-        <v>160</v>
+        <v>179</v>
       </c>
       <c r="E3" t="s">
-        <v>160</v>
+        <v>179</v>
       </c>
       <c r="F3" s="11" t="s">
         <v>129</v>
@@ -8967,19 +9160,19 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>164</v>
+        <v>183</v>
       </c>
       <c r="B4" t="s">
-        <v>165</v>
+        <v>184</v>
       </c>
       <c r="C4" t="s">
-        <v>166</v>
+        <v>185</v>
       </c>
       <c r="D4" t="s">
-        <v>160</v>
+        <v>179</v>
       </c>
       <c r="E4" t="s">
-        <v>160</v>
+        <v>179</v>
       </c>
       <c r="F4" s="11" t="s">
         <v>129</v>
@@ -8990,16 +9183,16 @@
         <v>44</v>
       </c>
       <c r="B5" t="s">
-        <v>167</v>
+        <v>186</v>
       </c>
       <c r="C5" t="s">
-        <v>168</v>
+        <v>187</v>
       </c>
       <c r="D5" t="s">
-        <v>160</v>
+        <v>179</v>
       </c>
       <c r="E5" t="s">
-        <v>160</v>
+        <v>179</v>
       </c>
       <c r="F5" s="11" t="s">
         <v>129</v>
@@ -9007,19 +9200,19 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>169</v>
+        <v>188</v>
       </c>
       <c r="B6" t="s">
-        <v>170</v>
+        <v>189</v>
       </c>
       <c r="C6" t="s">
-        <v>171</v>
+        <v>190</v>
       </c>
       <c r="D6" t="s">
-        <v>172</v>
+        <v>191</v>
       </c>
       <c r="E6" t="s">
-        <v>172</v>
+        <v>191</v>
       </c>
       <c r="F6" s="11" t="s">
         <v>129</v>
@@ -9027,19 +9220,19 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>173</v>
+        <v>192</v>
       </c>
       <c r="B7" t="s">
-        <v>174</v>
+        <v>193</v>
       </c>
       <c r="C7" t="s">
-        <v>175</v>
+        <v>194</v>
       </c>
       <c r="D7" t="s">
-        <v>172</v>
+        <v>191</v>
       </c>
       <c r="E7" t="s">
-        <v>172</v>
+        <v>191</v>
       </c>
       <c r="F7" s="11" t="s">
         <v>129</v>
@@ -9047,19 +9240,19 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>176</v>
+        <v>195</v>
       </c>
       <c r="B8" t="s">
-        <v>177</v>
+        <v>196</v>
       </c>
       <c r="C8" t="s">
-        <v>178</v>
+        <v>197</v>
       </c>
       <c r="D8" t="s">
-        <v>172</v>
+        <v>191</v>
       </c>
       <c r="E8" t="s">
-        <v>172</v>
+        <v>191</v>
       </c>
       <c r="F8" s="11" t="s">
         <v>129</v>

--- a/reports/progression-report.xlsx
+++ b/reports/progression-report.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1774" uniqueCount="198">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1809" uniqueCount="220">
   <si>
     <t>Персона</t>
   </si>
@@ -535,6 +535,72 @@
   </si>
   <si>
     <t>все названия совпадают с библиотекой</t>
+  </si>
+  <si>
+    <t>Форма лестницы сохраняется: "20/30/30/35" при оценке 3 → "20/32.5/32.5/37.5"</t>
+  </si>
+  <si>
+    <t>— (computeTemplateScale)</t>
+  </si>
+  <si>
+    <t>[20, 32.5, 32.5, 37.5], соотношение разминка/работа ≈0.571</t>
+  </si>
+  <si>
+    <t>[20, 32.5, 32.5, 37.5], соотношение ≈0.533</t>
+  </si>
+  <si>
+    <t>Разминка не догоняет рабочий вес: 10 тренировок подряд с оценкой 2, разминка/работа ≤ 0.9 на каждой</t>
+  </si>
+  <si>
+    <t>≤ 0.9 на всех 10 тренировках</t>
+  </si>
+  <si>
+    <t>худшее соотношение за 10 тренировок: 0.600</t>
+  </si>
+  <si>
+    <t>Подходы "30кг×12" и "35кг×12" (одинаковые повторения) остаются разными после масштабирования</t>
+  </si>
+  <si>
+    <t>kg3 ≠ kg4</t>
+  </si>
+  <si>
+    <t>kg3=32.5, kg4=37.5</t>
+  </si>
+  <si>
+    <t>Гравитрон: "-39 кг × 12", оценка 2 → вес менее отрицательный (меньше помощи)</t>
+  </si>
+  <si>
+    <t>&gt; -39 (ближе к нулю)</t>
+  </si>
+  <si>
+    <t>-37.5</t>
+  </si>
+  <si>
+    <t>Гравитрон: разминочная лестница масштабируется в ту же сторону (все подходы менее отрицательны, чем в шаблоне)</t>
+  </si>
+  <si>
+    <t>все подходы &gt; своего шаблонного значения</t>
+  </si>
+  <si>
+    <t>[-50, -45, -39, -39] → [-47.5, -42.5, -37.5, -37.5]</t>
+  </si>
+  <si>
+    <t>Откат (hardStreak): appliedPct=-15, вся лестница опускается пропорционально (каждый подход ниже шаблона)</t>
+  </si>
+  <si>
+    <t>hardStreak=true, appliedPct=-15, все подходы &lt; шаблона: [20, 30, 30, 35]</t>
+  </si>
+  <si>
+    <t>hardStreak=true, appliedPct=-15, результат: [17.5, 25, 25, 30]</t>
+  </si>
+  <si>
+    <t>Регресс на реальных данных (Ягодичный мост со штангой, история 60/100/120/120×20 → шаблон 20/30/30/35): точные числа</t>
+  </si>
+  <si>
+    <t>[85, 127.5, 127.5, 150], appliedPct=5, соотношение разминка/работа ≈0.567 (не 0.833 как у бага), подходы 3≠4</t>
+  </si>
+  <si>
+    <t>[85, 127.5, 127.5, 150], appliedPct=5, соотношение ≈0.567, kg3=127.5 kg4=150</t>
   </si>
   <si>
     <t>Название A</t>
@@ -1218,10 +1284,10 @@
         <v>6785</v>
       </c>
       <c r="E4">
-        <v>10393</v>
+        <v>10080</v>
       </c>
       <c r="F4">
-        <v>53.2</v>
+        <v>48.6</v>
       </c>
       <c r="G4">
         <v>0</v>
@@ -1244,10 +1310,10 @@
         <v>6785</v>
       </c>
       <c r="E5">
-        <v>9283</v>
+        <v>8945</v>
       </c>
       <c r="F5">
-        <v>36.8</v>
+        <v>31.8</v>
       </c>
       <c r="G5">
         <v>2</v>
@@ -1270,10 +1336,10 @@
         <v>5000</v>
       </c>
       <c r="E6">
-        <v>7240</v>
+        <v>6690</v>
       </c>
       <c r="F6">
-        <v>44.8</v>
+        <v>33.8</v>
       </c>
       <c r="G6">
         <v>0</v>
@@ -1478,46 +1544,46 @@
         <v>6785</v>
       </c>
       <c r="C4">
-        <v>7503</v>
+        <v>7278</v>
       </c>
       <c r="D4">
-        <v>7993</v>
+        <v>7668</v>
       </c>
       <c r="E4">
-        <v>8483</v>
+        <v>8158</v>
       </c>
       <c r="F4">
-        <v>8973</v>
+        <v>8648</v>
       </c>
       <c r="G4">
-        <v>9413</v>
+        <v>9138</v>
       </c>
       <c r="H4">
-        <v>9903</v>
+        <v>9628</v>
       </c>
       <c r="I4">
-        <v>10393</v>
+        <v>10080</v>
       </c>
       <c r="J4">
-        <v>10.6</v>
+        <v>7.3</v>
       </c>
       <c r="K4">
-        <v>6.5</v>
+        <v>5.4</v>
       </c>
       <c r="L4">
-        <v>6.1</v>
+        <v>6.4</v>
       </c>
       <c r="M4">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="N4">
-        <v>4.9</v>
+        <v>5.7</v>
       </c>
       <c r="O4">
-        <v>5.2</v>
+        <v>5.4</v>
       </c>
       <c r="P4">
-        <v>4.9</v>
+        <v>4.7</v>
       </c>
     </row>
     <row r="5" spans="1:16" x14ac:dyDescent="0.25">
@@ -1528,46 +1594,46 @@
         <v>6785</v>
       </c>
       <c r="C5">
-        <v>7363</v>
+        <v>7088</v>
       </c>
       <c r="D5">
-        <v>7560</v>
+        <v>7323</v>
       </c>
       <c r="E5">
-        <v>7960</v>
+        <v>7685</v>
       </c>
       <c r="F5">
-        <v>8323</v>
+        <v>8085</v>
       </c>
       <c r="G5">
-        <v>8685</v>
+        <v>8410</v>
       </c>
       <c r="H5">
-        <v>8883</v>
+        <v>8645</v>
       </c>
       <c r="I5">
-        <v>9283</v>
+        <v>8945</v>
       </c>
       <c r="J5">
-        <v>8.5</v>
+        <v>4.5</v>
       </c>
       <c r="K5">
-        <v>2.7</v>
+        <v>3.3</v>
       </c>
       <c r="L5">
-        <v>5.3</v>
+        <v>5</v>
       </c>
       <c r="M5">
-        <v>4.6</v>
+        <v>5.2</v>
       </c>
       <c r="N5">
-        <v>4.4</v>
+        <v>4</v>
       </c>
       <c r="O5">
-        <v>2.3</v>
+        <v>2.8</v>
       </c>
       <c r="P5">
-        <v>4.5</v>
+        <v>3.5</v>
       </c>
     </row>
     <row r="6" spans="1:16" x14ac:dyDescent="0.25">
@@ -1578,46 +1644,46 @@
         <v>5000</v>
       </c>
       <c r="C6">
-        <v>5570</v>
+        <v>5195</v>
       </c>
       <c r="D6">
-        <v>5865</v>
+        <v>5415</v>
       </c>
       <c r="E6">
-        <v>6160</v>
+        <v>5710</v>
       </c>
       <c r="F6">
-        <v>6455</v>
+        <v>5905</v>
       </c>
       <c r="G6">
-        <v>6750</v>
+        <v>6200</v>
       </c>
       <c r="H6">
-        <v>6945</v>
+        <v>6495</v>
       </c>
       <c r="I6">
-        <v>7240</v>
+        <v>6690</v>
       </c>
       <c r="J6">
-        <v>11.4</v>
+        <v>3.9</v>
       </c>
       <c r="K6">
-        <v>5.3</v>
+        <v>4.2</v>
       </c>
       <c r="L6">
+        <v>5.4</v>
+      </c>
+      <c r="M6">
+        <v>3.4</v>
+      </c>
+      <c r="N6">
         <v>5</v>
       </c>
-      <c r="M6">
+      <c r="O6">
         <v>4.8</v>
       </c>
-      <c r="N6">
-        <v>4.6</v>
-      </c>
-      <c r="O6">
-        <v>2.9</v>
-      </c>
       <c r="P6">
-        <v>4.2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.25">
@@ -8289,7 +8355,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E46"/>
+  <dimension ref="A1:E53"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="45" customWidth="1"/>
@@ -9078,6 +9144,125 @@
         <v>172</v>
       </c>
       <c r="E46" s="11" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A47" t="s">
+        <v>173</v>
+      </c>
+      <c r="B47" t="s">
+        <v>174</v>
+      </c>
+      <c r="C47" t="s">
+        <v>175</v>
+      </c>
+      <c r="D47" t="s">
+        <v>176</v>
+      </c>
+      <c r="E47" s="11" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A48" t="s">
+        <v>177</v>
+      </c>
+      <c r="B48" t="s">
+        <v>174</v>
+      </c>
+      <c r="C48" t="s">
+        <v>178</v>
+      </c>
+      <c r="D48" t="s">
+        <v>179</v>
+      </c>
+      <c r="E48" s="11" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A49" t="s">
+        <v>180</v>
+      </c>
+      <c r="B49" t="s">
+        <v>174</v>
+      </c>
+      <c r="C49" t="s">
+        <v>181</v>
+      </c>
+      <c r="D49" t="s">
+        <v>182</v>
+      </c>
+      <c r="E49" s="11" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A50" t="s">
+        <v>183</v>
+      </c>
+      <c r="B50" t="s">
+        <v>174</v>
+      </c>
+      <c r="C50" t="s">
+        <v>184</v>
+      </c>
+      <c r="D50" t="s">
+        <v>185</v>
+      </c>
+      <c r="E50" s="11" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A51" t="s">
+        <v>186</v>
+      </c>
+      <c r="B51" t="s">
+        <v>174</v>
+      </c>
+      <c r="C51" t="s">
+        <v>187</v>
+      </c>
+      <c r="D51" t="s">
+        <v>188</v>
+      </c>
+      <c r="E51" s="11" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A52" t="s">
+        <v>189</v>
+      </c>
+      <c r="B52" t="s">
+        <v>174</v>
+      </c>
+      <c r="C52" t="s">
+        <v>190</v>
+      </c>
+      <c r="D52" t="s">
+        <v>191</v>
+      </c>
+      <c r="E52" s="11" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A53" t="s">
+        <v>192</v>
+      </c>
+      <c r="B53" t="s">
+        <v>174</v>
+      </c>
+      <c r="C53" t="s">
+        <v>193</v>
+      </c>
+      <c r="D53" t="s">
+        <v>194</v>
+      </c>
+      <c r="E53" s="11" t="s">
         <v>129</v>
       </c>
     </row>
@@ -9100,13 +9285,13 @@
   <sheetData>
     <row r="1" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>173</v>
+        <v>195</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>174</v>
+        <v>196</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>175</v>
+        <v>197</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>124</v>
@@ -9120,19 +9305,19 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>176</v>
+        <v>198</v>
       </c>
       <c r="B2" t="s">
-        <v>177</v>
+        <v>199</v>
       </c>
       <c r="C2" t="s">
-        <v>178</v>
+        <v>200</v>
       </c>
       <c r="D2" t="s">
-        <v>179</v>
+        <v>201</v>
       </c>
       <c r="E2" t="s">
-        <v>179</v>
+        <v>201</v>
       </c>
       <c r="F2" s="11" t="s">
         <v>129</v>
@@ -9140,19 +9325,19 @@
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>180</v>
+        <v>202</v>
       </c>
       <c r="B3" t="s">
-        <v>181</v>
+        <v>203</v>
       </c>
       <c r="C3" t="s">
-        <v>182</v>
+        <v>204</v>
       </c>
       <c r="D3" t="s">
-        <v>179</v>
+        <v>201</v>
       </c>
       <c r="E3" t="s">
-        <v>179</v>
+        <v>201</v>
       </c>
       <c r="F3" s="11" t="s">
         <v>129</v>
@@ -9160,19 +9345,19 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>183</v>
+        <v>205</v>
       </c>
       <c r="B4" t="s">
-        <v>184</v>
+        <v>206</v>
       </c>
       <c r="C4" t="s">
-        <v>185</v>
+        <v>207</v>
       </c>
       <c r="D4" t="s">
-        <v>179</v>
+        <v>201</v>
       </c>
       <c r="E4" t="s">
-        <v>179</v>
+        <v>201</v>
       </c>
       <c r="F4" s="11" t="s">
         <v>129</v>
@@ -9183,16 +9368,16 @@
         <v>44</v>
       </c>
       <c r="B5" t="s">
-        <v>186</v>
+        <v>208</v>
       </c>
       <c r="C5" t="s">
-        <v>187</v>
+        <v>209</v>
       </c>
       <c r="D5" t="s">
-        <v>179</v>
+        <v>201</v>
       </c>
       <c r="E5" t="s">
-        <v>179</v>
+        <v>201</v>
       </c>
       <c r="F5" s="11" t="s">
         <v>129</v>
@@ -9200,19 +9385,19 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>188</v>
+        <v>210</v>
       </c>
       <c r="B6" t="s">
-        <v>189</v>
+        <v>211</v>
       </c>
       <c r="C6" t="s">
-        <v>190</v>
+        <v>212</v>
       </c>
       <c r="D6" t="s">
-        <v>191</v>
+        <v>213</v>
       </c>
       <c r="E6" t="s">
-        <v>191</v>
+        <v>213</v>
       </c>
       <c r="F6" s="11" t="s">
         <v>129</v>
@@ -9220,19 +9405,19 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>192</v>
+        <v>214</v>
       </c>
       <c r="B7" t="s">
-        <v>193</v>
+        <v>215</v>
       </c>
       <c r="C7" t="s">
-        <v>194</v>
+        <v>216</v>
       </c>
       <c r="D7" t="s">
-        <v>191</v>
+        <v>213</v>
       </c>
       <c r="E7" t="s">
-        <v>191</v>
+        <v>213</v>
       </c>
       <c r="F7" s="11" t="s">
         <v>129</v>
@@ -9240,19 +9425,19 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>195</v>
+        <v>217</v>
       </c>
       <c r="B8" t="s">
-        <v>196</v>
+        <v>218</v>
       </c>
       <c r="C8" t="s">
-        <v>197</v>
+        <v>219</v>
       </c>
       <c r="D8" t="s">
-        <v>191</v>
+        <v>213</v>
       </c>
       <c r="E8" t="s">
-        <v>191</v>
+        <v>213</v>
       </c>
       <c r="F8" s="11" t="s">
         <v>129</v>

--- a/reports/progression-report.xlsx
+++ b/reports/progression-report.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1809" uniqueCount="220">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1814" uniqueCount="223">
   <si>
     <t>Персона</t>
   </si>
@@ -601,6 +601,15 @@
   </si>
   <si>
     <t>[85, 127.5, 127.5, 150], appliedPct=5, соотношение ≈0.567, kg3=127.5 kg4=150</t>
+  </si>
+  <si>
+    <t>Удаление единственной тренировки упражнения → холодный старт при следующем появлении (agg отсутствует, scale=null)</t>
+  </si>
+  <si>
+    <t>до удаления: scale посчитан (не холодный старт); после: agg отсутствует → холодный старт</t>
+  </si>
+  <si>
+    <t>до: scale=1.050; после: agg отсутствует</t>
   </si>
   <si>
     <t>Название A</t>
@@ -8355,7 +8364,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E53"/>
+  <dimension ref="A1:E54"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="45" customWidth="1"/>
@@ -9263,6 +9272,23 @@
         <v>194</v>
       </c>
       <c r="E53" s="11" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A54" t="s">
+        <v>195</v>
+      </c>
+      <c r="B54" t="s">
+        <v>174</v>
+      </c>
+      <c r="C54" t="s">
+        <v>196</v>
+      </c>
+      <c r="D54" t="s">
+        <v>197</v>
+      </c>
+      <c r="E54" s="11" t="s">
         <v>129</v>
       </c>
     </row>
@@ -9285,13 +9311,13 @@
   <sheetData>
     <row r="1" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>124</v>
@@ -9305,19 +9331,19 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="B2" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="C2" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="D2" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="E2" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="F2" s="11" t="s">
         <v>129</v>
@@ -9325,19 +9351,19 @@
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="B3" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="C3" t="s">
+        <v>207</v>
+      </c>
+      <c r="D3" t="s">
         <v>204</v>
       </c>
-      <c r="D3" t="s">
-        <v>201</v>
-      </c>
       <c r="E3" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="F3" s="11" t="s">
         <v>129</v>
@@ -9345,19 +9371,19 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="B4" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="C4" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="D4" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="E4" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="F4" s="11" t="s">
         <v>129</v>
@@ -9368,16 +9394,16 @@
         <v>44</v>
       </c>
       <c r="B5" t="s">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="C5" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="D5" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="E5" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="F5" s="11" t="s">
         <v>129</v>
@@ -9385,19 +9411,19 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="B6" t="s">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="C6" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="D6" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="E6" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="F6" s="11" t="s">
         <v>129</v>
@@ -9405,19 +9431,19 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="B7" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="C7" t="s">
+        <v>219</v>
+      </c>
+      <c r="D7" t="s">
         <v>216</v>
       </c>
-      <c r="D7" t="s">
-        <v>213</v>
-      </c>
       <c r="E7" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="F7" s="11" t="s">
         <v>129</v>
@@ -9425,19 +9451,19 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="B8" t="s">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="C8" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="D8" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="E8" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="F8" s="11" t="s">
         <v>129</v>
